--- a/mass_production_tool/range_test_sample.xlsx
+++ b/mass_production_tool/range_test_sample.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\GitHub\Mass_produc\mass_produc\mass_production_tool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49A70D23-C9AE-4BD4-B8F4-80B7F7C93FF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{391762AC-DCF3-4836-BA11-C3C28280BF7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="8880" yWindow="6600" windowWidth="34560" windowHeight="18600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,18 +28,9 @@
     <t>Description</t>
   </si>
   <si>
-    <t>MIN  ( int )</t>
-  </si>
-  <si>
-    <t>MAX  ( int )</t>
-  </si>
-  <si>
     <t>DELAY ms</t>
   </si>
   <si>
-    <t>RETURN  ( int )</t>
-  </si>
-  <si>
     <t>PASS COUNT</t>
   </si>
   <si>
@@ -107,6 +98,18 @@
   </si>
   <si>
     <t>Range item 10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MIN  </t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">MAX </t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">RETURN  </t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -366,33 +369,33 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C2" s="2">
         <v>0</v>
@@ -418,10 +421,10 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C3" s="2">
         <v>10</v>
@@ -447,10 +450,10 @@
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C4" s="2">
         <v>20</v>
@@ -476,10 +479,10 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C5" s="2">
         <v>30</v>
@@ -505,10 +508,10 @@
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C6" s="2">
         <v>40</v>
@@ -534,10 +537,10 @@
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="2" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C7" s="2">
         <v>50</v>
@@ -563,10 +566,10 @@
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="2" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C8" s="2">
         <v>60</v>
@@ -592,10 +595,10 @@
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C9" s="2">
         <v>70</v>
@@ -621,10 +624,10 @@
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C10" s="2">
         <v>80</v>
@@ -650,10 +653,10 @@
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C11" s="2">
         <v>90</v>
@@ -679,10 +682,10 @@
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C12" s="2">
         <v>0</v>
@@ -708,10 +711,10 @@
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C13" s="2">
         <v>10</v>
@@ -737,10 +740,10 @@
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C14" s="2">
         <v>20</v>
@@ -766,10 +769,10 @@
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C15" s="2">
         <v>30</v>
@@ -795,10 +798,10 @@
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C16" s="2">
         <v>40</v>
@@ -824,10 +827,10 @@
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="2" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C17" s="2">
         <v>50</v>
@@ -853,10 +856,10 @@
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="2" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C18" s="2">
         <v>60</v>
@@ -882,10 +885,10 @@
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C19" s="2">
         <v>70</v>
@@ -911,10 +914,10 @@
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C20" s="2">
         <v>80</v>
@@ -940,10 +943,10 @@
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C21" s="2">
         <v>90</v>
@@ -969,10 +972,10 @@
     </row>
     <row r="22" spans="1:9">
       <c r="A22" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C22" s="2">
         <v>0</v>
@@ -998,10 +1001,10 @@
     </row>
     <row r="23" spans="1:9">
       <c r="A23" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C23" s="2">
         <v>10</v>
@@ -1027,10 +1030,10 @@
     </row>
     <row r="24" spans="1:9">
       <c r="A24" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C24" s="2">
         <v>20</v>
@@ -1056,10 +1059,10 @@
     </row>
     <row r="25" spans="1:9">
       <c r="A25" s="2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C25" s="2">
         <v>30</v>
@@ -1085,10 +1088,10 @@
     </row>
     <row r="26" spans="1:9">
       <c r="A26" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C26" s="2">
         <v>40</v>
@@ -1114,10 +1117,10 @@
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="2" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C27" s="2">
         <v>50</v>
@@ -1143,10 +1146,10 @@
     </row>
     <row r="28" spans="1:9">
       <c r="A28" s="2" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C28" s="2">
         <v>60</v>
@@ -1172,10 +1175,10 @@
     </row>
     <row r="29" spans="1:9">
       <c r="A29" s="2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C29" s="2">
         <v>70</v>
@@ -1201,10 +1204,10 @@
     </row>
     <row r="30" spans="1:9">
       <c r="A30" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C30" s="2">
         <v>80</v>
@@ -1230,10 +1233,10 @@
     </row>
     <row r="31" spans="1:9">
       <c r="A31" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C31" s="2">
         <v>90</v>
@@ -1259,10 +1262,10 @@
     </row>
     <row r="32" spans="1:9">
       <c r="A32" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C32" s="2">
         <v>0</v>
@@ -1288,10 +1291,10 @@
     </row>
     <row r="33" spans="1:9">
       <c r="A33" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C33" s="2">
         <v>10</v>
@@ -1317,10 +1320,10 @@
     </row>
     <row r="34" spans="1:9">
       <c r="A34" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C34" s="2">
         <v>20</v>
@@ -1346,10 +1349,10 @@
     </row>
     <row r="35" spans="1:9">
       <c r="A35" s="2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C35" s="2">
         <v>30</v>
@@ -1375,10 +1378,10 @@
     </row>
     <row r="36" spans="1:9">
       <c r="A36" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C36" s="2">
         <v>40</v>
@@ -1404,10 +1407,10 @@
     </row>
     <row r="37" spans="1:9">
       <c r="A37" s="2" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C37" s="2">
         <v>50</v>
@@ -1433,10 +1436,10 @@
     </row>
     <row r="38" spans="1:9">
       <c r="A38" s="2" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C38" s="2">
         <v>60</v>
@@ -1462,10 +1465,10 @@
     </row>
     <row r="39" spans="1:9">
       <c r="A39" s="2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C39" s="2">
         <v>70</v>
@@ -1491,10 +1494,10 @@
     </row>
     <row r="40" spans="1:9">
       <c r="A40" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C40" s="2">
         <v>80</v>
@@ -1520,10 +1523,10 @@
     </row>
     <row r="41" spans="1:9">
       <c r="A41" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C41" s="2">
         <v>90</v>
@@ -1549,10 +1552,10 @@
     </row>
     <row r="42" spans="1:9">
       <c r="A42" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C42" s="2">
         <v>0</v>
@@ -1578,10 +1581,10 @@
     </row>
     <row r="43" spans="1:9">
       <c r="A43" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C43" s="2">
         <v>10</v>
@@ -1607,10 +1610,10 @@
     </row>
     <row r="44" spans="1:9">
       <c r="A44" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C44" s="2">
         <v>20</v>
@@ -1636,10 +1639,10 @@
     </row>
     <row r="45" spans="1:9">
       <c r="A45" s="2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C45" s="2">
         <v>30</v>
@@ -1665,10 +1668,10 @@
     </row>
     <row r="46" spans="1:9">
       <c r="A46" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C46" s="2">
         <v>40</v>
@@ -1694,10 +1697,10 @@
     </row>
     <row r="47" spans="1:9">
       <c r="A47" s="2" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C47" s="2">
         <v>50</v>
@@ -1723,10 +1726,10 @@
     </row>
     <row r="48" spans="1:9">
       <c r="A48" s="2" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C48" s="2">
         <v>60</v>
@@ -1752,10 +1755,10 @@
     </row>
     <row r="49" spans="1:9">
       <c r="A49" s="2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C49" s="2">
         <v>70</v>
@@ -1781,10 +1784,10 @@
     </row>
     <row r="50" spans="1:9">
       <c r="A50" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C50" s="2">
         <v>80</v>
@@ -1810,10 +1813,10 @@
     </row>
     <row r="51" spans="1:9">
       <c r="A51" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C51" s="2">
         <v>90</v>
